--- a/sheets/민요/검수/풍년 노래.xlsx
+++ b/sheets/민요/검수/풍년 노래.xlsx
@@ -4,15 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -21,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -51,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +176,57 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3296,8 +3426,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U16"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3320,887 +3454,829 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">풍년 노래 — 민요채보-3/풍년 노래.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">풍년 노래</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">열</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">징</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">맞</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 仲</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="19"/>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I4" s="19"/>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K4" s="19"/>
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O4" s="19"/>
+      <c r="P4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="S4" s="19"/>
+      <c r="T4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U4" s="19"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 仲</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="20"/>
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O5" s="20"/>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="S5" s="20"/>
+      <c r="T5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="U5" s="20"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="18"/>
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="I6" s="18"/>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K6" s="18"/>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M6" s="18"/>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="P6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="S6" s="18"/>
+      <c r="T6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K7" s="19"/>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="N7" s="16"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="Q7" s="19"/>
+      <c r="R7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S7" s="19"/>
+      <c r="T7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U7" s="19"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K8" s="20"/>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="P8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="T8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
     </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">풍년 노래 — 민요채보-3/풍년 노래.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="9"/>
+    <row r="10" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B10">
+        <is>
+          <t xml:space="preserve">풍년 노래</t>
+        </is>
+      </c>
+      <c s="8" r="C10"/>
+      <c s="8" r="D10"/>
+      <c s="8" r="E10"/>
+      <c s="8" r="F10"/>
+      <c s="8" r="G10"/>
+      <c s="8" r="H10"/>
+      <c s="8" r="I10"/>
+      <c s="8" r="J10"/>
+      <c s="8" r="K10"/>
+      <c s="8" r="L10"/>
+      <c s="8" r="M10"/>
+      <c s="8" r="N10"/>
+      <c s="8" r="O10"/>
+      <c s="8" r="P10"/>
+      <c s="8" r="Q10"/>
+      <c s="8" r="R10"/>
+      <c s="8" r="S10"/>
+      <c s="8" r="T10"/>
+      <c s="8" r="U10"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="17"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">짜</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="R11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 姑</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="S11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="T11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="U11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="17"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S12" s="19"/>
+      <c r="T12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U12" s="19"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="17"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="Q13" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="R13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="S13" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="T13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="U13" s="20"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="17"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S14" s="18"/>
+      <c r="T14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U14" s="18"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="17"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="S15" s="19"/>
+      <c r="T15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="U15" s="19"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="17"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q16" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
+      <c r="R16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S16" s="20"/>
+      <c r="T16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U16" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B10:U10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="8" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/풍년 노래.xlsx
+++ b/sheets/민요/검수/풍년 노래.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/풍년 노래.xlsx
+++ b/sheets/민요/검수/풍년 노래.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5954,124 +5992,124 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">풍년 노래</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">참</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">질</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">호</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">호</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
       </c>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="R3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="S3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6079,93 +6117,93 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">덩</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">악</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="P4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="R4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="R4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="S4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">혜</t>
         </is>
@@ -6173,1039 +6211,1039 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">춤</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">평</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="O5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">평</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S5" s="9"/>
+      <c r="P5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S5" s="25"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I6" s="26"/>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="M6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="O6" s="10" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="O6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="S6" s="10"/>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="S6" s="26"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">잭</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="M7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">멋</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P7" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q7" s="11" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="R7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="S7" s="8"/>
+      <c r="S7" s="24"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">잭</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K8" s="25"/>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O8" s="9"/>
-      <c r="P8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="Q8" s="9" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O8" s="25"/>
+      <c r="P8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="R8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S8" s="9"/>
+      <c r="R8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E9" s="25"/>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G9" s="25"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I9" s="25"/>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K9" s="25"/>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="M9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">었</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="O9" s="9"/>
-      <c r="P9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="S9" s="9"/>
+      <c r="N9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="O9" s="25"/>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="S9" s="25"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E10" s="26"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G10" s="26"/>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K10" s="26"/>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="S10" s="10"/>
+      <c r="N10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="O10" s="26"/>
+      <c r="P10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="S10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="24"/>
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="I11" s="24"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">괭</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="Q11" s="8" t="inlineStr">
+      <c r="Q11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="R11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="S11" s="8"/>
+      <c r="S11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G12" s="25"/>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I12" s="25"/>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O12" s="9" t="inlineStr">
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="S12" s="9"/>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="S12" s="25"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="S13" s="9"/>
+      <c r="S13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">창</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="M14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="O14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="S14" s="10"/>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="S14" s="26"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">깍</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G15" s="24"/>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I15" s="24"/>
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">칭</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="17" t="inlineStr">
+      <c r="N15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O15" s="24"/>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S15" s="8"/>
+      <c r="S15" s="24"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">깍</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="O16" s="9"/>
-      <c r="P16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S16" s="9"/>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G16" s="25"/>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I16" s="25"/>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K16" s="25"/>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="M16" s="25"/>
+      <c r="N16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="O16" s="25"/>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 無
 姑</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="O17" s="9"/>
-      <c r="P17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="S17" s="9"/>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E17" s="25"/>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G17" s="25"/>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I17" s="25"/>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K17" s="25"/>
+      <c r="L17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="M17" s="25"/>
+      <c r="N17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="O17" s="25"/>
+      <c r="P17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="S17" s="25"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="S18" s="10"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G18" s="26"/>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I18" s="26"/>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K18" s="26"/>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="M18" s="26"/>
+      <c r="N18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="O18" s="26"/>
+      <c r="P18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="S18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/풍년 노래.xlsx
+++ b/sheets/민요/검수/풍년 노래.xlsx
@@ -5967,30 +5967,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="S5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="S6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="S7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="S8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="S9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="S10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="S12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="S13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="S14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="S15" s="24"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="S16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="S17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>

--- a/sheets/민요/검수/풍년 노래.xlsx
+++ b/sheets/민요/검수/풍년 노래.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +238,21 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6023,7 +6043,7 @@
 仲</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -6033,7 +6053,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">참</t>
         </is>
@@ -6044,7 +6064,7 @@
 潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
@@ -6055,7 +6075,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">질</t>
         </is>
@@ -6066,7 +6086,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">호</t>
         </is>
@@ -6077,7 +6097,7 @@
 仲</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
@@ -6087,7 +6107,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">호</t>
         </is>
@@ -6098,7 +6118,7 @@
 姑</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="inlineStr">
+      <c r="Q3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
@@ -6109,7 +6129,7 @@
 潢</t>
         </is>
       </c>
-      <c r="S3" s="24" t="inlineStr">
+      <c r="S3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6123,7 +6143,7 @@
 仲</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -6133,7 +6153,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -6143,7 +6163,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">덩</t>
         </is>
@@ -6153,7 +6173,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -6163,7 +6183,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
@@ -6173,7 +6193,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">악</t>
         </is>
@@ -6183,7 +6203,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
@@ -6193,7 +6213,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -6203,7 +6223,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S4" s="25" t="inlineStr">
+      <c r="S4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">혜</t>
         </is>
@@ -6216,13 +6236,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C5" s="25"/>
+      <c r="C5" s="30"/>
       <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -6233,7 +6253,7 @@
 潢</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">춤</t>
         </is>
@@ -6243,7 +6263,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -6253,7 +6273,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">평</t>
         </is>
@@ -6263,7 +6283,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -6273,7 +6293,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O5" s="25" t="inlineStr">
+      <c r="O5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">평</t>
         </is>
@@ -6283,13 +6303,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q5" s="25"/>
+      <c r="Q5" s="30"/>
       <c r="R5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S5" s="25"/>
+      <c r="S5" s="30"/>
     </row>
     <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
@@ -6298,19 +6318,19 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="26"/>
+      <c r="C6" s="31"/>
       <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E6" s="26"/>
+      <c r="E6" s="31"/>
       <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -6320,13 +6340,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I6" s="26"/>
+      <c r="I6" s="31"/>
       <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="K6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -6336,7 +6356,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M6" s="26" t="inlineStr">
+      <c r="M6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -6346,7 +6366,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O6" s="26" t="inlineStr">
+      <c r="O6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -6356,13 +6376,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q6" s="26"/>
+      <c r="Q6" s="31"/>
       <c r="R6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S6" s="26"/>
+      <c r="S6" s="31"/>
     </row>
     <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
@@ -6371,7 +6391,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -6381,7 +6401,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">잭</t>
         </is>
@@ -6392,7 +6412,7 @@
 仲</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
@@ -6403,7 +6423,7 @@
 仲</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -6413,7 +6433,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K7" s="24" t="inlineStr">
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6424,7 +6444,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M7" s="24" t="inlineStr">
+      <c r="M7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">멋</t>
         </is>
@@ -6434,7 +6454,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O7" s="24" t="inlineStr">
+      <c r="O7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6444,7 +6464,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q7" s="22" t="inlineStr">
+      <c r="Q7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
@@ -6455,7 +6475,7 @@
 仲</t>
         </is>
       </c>
-      <c r="S7" s="24"/>
+      <c r="S7" s="29"/>
     </row>
     <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
@@ -6464,7 +6484,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -6474,7 +6494,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">잭</t>
         </is>
@@ -6484,7 +6504,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -6494,7 +6514,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -6504,13 +6524,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K8" s="25"/>
+      <c r="K8" s="30"/>
       <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M8" s="25" t="inlineStr">
+      <c r="M8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -6520,13 +6540,13 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O8" s="25"/>
+      <c r="O8" s="30"/>
       <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="Q8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -6536,7 +6556,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S8" s="25"/>
+      <c r="S8" s="30"/>
     </row>
     <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
@@ -6546,7 +6566,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
@@ -6556,31 +6576,31 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E9" s="25"/>
+      <c r="E9" s="30"/>
       <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="30"/>
       <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I9" s="25"/>
+      <c r="I9" s="30"/>
       <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K9" s="25"/>
+      <c r="K9" s="30"/>
       <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M9" s="25" t="inlineStr">
+      <c r="M9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">었</t>
         </is>
@@ -6590,19 +6610,19 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O9" s="25"/>
+      <c r="O9" s="30"/>
       <c r="P9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q9" s="25"/>
+      <c r="Q9" s="30"/>
       <c r="R9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S9" s="25"/>
+      <c r="S9" s="30"/>
     </row>
     <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
@@ -6611,7 +6631,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -6621,31 +6641,31 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="26"/>
+      <c r="I10" s="31"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K10" s="26"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M10" s="26" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -6655,19 +6675,19 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O10" s="26"/>
+      <c r="O10" s="31"/>
       <c r="P10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q10" s="26"/>
+      <c r="Q10" s="31"/>
       <c r="R10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S10" s="26"/>
+      <c r="S10" s="31"/>
     </row>
     <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
@@ -6677,7 +6697,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6688,7 +6708,7 @@
 姑</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
@@ -6698,20 +6718,20 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G11" s="24"/>
+      <c r="G11" s="29"/>
       <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="24"/>
+      <c r="I11" s="29"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">괭</t>
         </is>
@@ -6722,7 +6742,7 @@
 仲</t>
         </is>
       </c>
-      <c r="M11" s="22" t="inlineStr">
+      <c r="M11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -6733,7 +6753,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O11" s="24" t="inlineStr">
+      <c r="O11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -6744,7 +6764,7 @@
 仲</t>
         </is>
       </c>
-      <c r="Q11" s="24" t="inlineStr">
+      <c r="Q11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6755,7 +6775,7 @@
 仲</t>
         </is>
       </c>
-      <c r="S11" s="24"/>
+      <c r="S11" s="29"/>
     </row>
     <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
@@ -6764,13 +6784,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C12" s="25"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -6780,19 +6800,19 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="25"/>
+      <c r="G12" s="30"/>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I12" s="25"/>
+      <c r="I12" s="30"/>
       <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K12" s="25" t="inlineStr">
+      <c r="K12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -6802,7 +6822,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="25" t="inlineStr">
+      <c r="M12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
@@ -6812,7 +6832,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O12" s="25" t="inlineStr">
+      <c r="O12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
@@ -6822,13 +6842,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q12" s="25"/>
+      <c r="Q12" s="30"/>
       <c r="R12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S12" s="25"/>
+      <c r="S12" s="30"/>
     </row>
     <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
@@ -6837,7 +6857,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
@@ -6848,7 +6868,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -6858,20 +6878,20 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="30"/>
       <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -6882,7 +6902,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -6892,7 +6912,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O13" s="25" t="inlineStr">
+      <c r="O13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -6902,14 +6922,14 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="30"/>
       <c r="R13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="S13" s="25"/>
+      <c r="S13" s="30"/>
     </row>
     <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
@@ -6918,7 +6938,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -6928,25 +6948,25 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="31"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="31"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K14" s="26" t="inlineStr">
+      <c r="K14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">창</t>
         </is>
@@ -6956,7 +6976,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M14" s="26" t="inlineStr">
+      <c r="M14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -6966,7 +6986,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O14" s="26" t="inlineStr">
+      <c r="O14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6976,13 +6996,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q14" s="26"/>
+      <c r="Q14" s="31"/>
       <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S14" s="26"/>
+      <c r="S14" s="31"/>
     </row>
     <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
@@ -6991,7 +7011,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -7001,7 +7021,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">깍</t>
         </is>
@@ -7011,19 +7031,19 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G15" s="24"/>
+      <c r="G15" s="29"/>
       <c r="H15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I15" s="24"/>
+      <c r="I15" s="29"/>
       <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K15" s="24" t="inlineStr">
+      <c r="K15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">칭</t>
         </is>
@@ -7034,7 +7054,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M15" s="24" t="inlineStr">
+      <c r="M15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -7044,19 +7064,19 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O15" s="24"/>
+      <c r="O15" s="29"/>
       <c r="P15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q15" s="24"/>
+      <c r="Q15" s="29"/>
       <c r="R15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S15" s="24"/>
+      <c r="S15" s="29"/>
     </row>
     <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
@@ -7065,7 +7085,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -7075,7 +7095,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">깍</t>
         </is>
@@ -7085,43 +7105,43 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G16" s="25"/>
+      <c r="G16" s="30"/>
       <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I16" s="25"/>
+      <c r="I16" s="30"/>
       <c r="J16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K16" s="25"/>
+      <c r="K16" s="30"/>
       <c r="L16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M16" s="25"/>
+      <c r="M16" s="30"/>
       <c r="N16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O16" s="25"/>
+      <c r="O16" s="30"/>
       <c r="P16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q16" s="25"/>
+      <c r="Q16" s="30"/>
       <c r="R16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S16" s="25"/>
+      <c r="S16" s="30"/>
     </row>
     <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
@@ -7132,7 +7152,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -7142,49 +7162,49 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E17" s="25"/>
+      <c r="E17" s="30"/>
       <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="30"/>
       <c r="H17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I17" s="25"/>
+      <c r="I17" s="30"/>
       <c r="J17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K17" s="25"/>
+      <c r="K17" s="30"/>
       <c r="L17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M17" s="25"/>
+      <c r="M17" s="30"/>
       <c r="N17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O17" s="25"/>
+      <c r="O17" s="30"/>
       <c r="P17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q17" s="25"/>
+      <c r="Q17" s="30"/>
       <c r="R17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S17" s="25"/>
+      <c r="S17" s="30"/>
     </row>
     <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
@@ -7195,55 +7215,55 @@
 仲</t>
         </is>
       </c>
-      <c r="C18" s="26"/>
+      <c r="C18" s="31"/>
       <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="26"/>
+      <c r="E18" s="31"/>
       <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="26"/>
+      <c r="G18" s="31"/>
       <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="26"/>
+      <c r="I18" s="31"/>
       <c r="J18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="26"/>
+      <c r="K18" s="31"/>
       <c r="L18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M18" s="26"/>
+      <c r="M18" s="31"/>
       <c r="N18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O18" s="26"/>
+      <c r="O18" s="31"/>
       <c r="P18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q18" s="26"/>
+      <c r="Q18" s="31"/>
       <c r="R18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S18" s="26"/>
+      <c r="S18" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/풍년 노래.xlsx
+++ b/sheets/민요/검수/풍년 노래.xlsx
@@ -950,10 +950,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/풍년 노래.xlsx
+++ b/sheets/민요/검수/풍년 노래.xlsx
@@ -896,17 +896,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -1023,7 +1023,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1081,6 +1081,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3989,506 +4033,506 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:U10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="71.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="71.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="7" t="s">
+      <c r="M3" s="21"/>
+      <c r="N3" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="S3" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="T3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U3" s="19" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="71.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="22" t="s">
         <v>202</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M4" s="11"/>
-      <c r="N4" s="7" t="s">
+      <c r="M4" s="22"/>
+      <c r="N4" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="22" t="s">
         <v>202</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="S4" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="T4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="U4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="71.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="U4" s="22"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="8"/>
-      <c r="N5" s="7" t="s">
+      <c r="M5" s="19"/>
+      <c r="N5" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="Q5" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="R5" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="S5" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="T5" s="7" t="s">
+      <c r="T5" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="U5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="71.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="U5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B6" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="24"/>
+      <c r="F6" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="24"/>
+      <c r="J6" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="K6" s="13"/>
-      <c r="L6" s="7" t="s">
+      <c r="K6" s="24"/>
+      <c r="L6" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="7" t="s">
+      <c r="M6" s="24"/>
+      <c r="N6" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="O6" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Q6" s="13" t="s">
+      <c r="Q6" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="R6" s="7" t="s">
+      <c r="R6" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="S6" s="13" t="s">
+      <c r="S6" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="T6" s="7" t="s">
+      <c r="T6" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="U6" s="13"/>
-    </row>
-    <row r="7" customFormat="false" ht="71.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="U6" s="24"/>
+    </row>
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="Q7" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="R7" s="7" t="s">
+      <c r="R7" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="S7" s="8" t="s">
+      <c r="S7" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="T7" s="7" t="s">
+      <c r="T7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="U7" s="8" t="s">
+      <c r="U7" s="19" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="71.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="P8" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="12" t="s">
+      <c r="Q8" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="R8" s="7" t="s">
+      <c r="R8" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="S8" s="11"/>
-      <c r="T8" s="7" t="s">
+      <c r="S8" s="22"/>
+      <c r="T8" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="U8" s="11"/>
-    </row>
-    <row r="9" customFormat="false" ht="71.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="U8" s="22"/>
+    </row>
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B9" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="7" t="s">
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="7" t="s">
+      <c r="O9" s="19"/>
+      <c r="P9" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="R9" s="7" t="s">
+      <c r="R9" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="S9" s="8"/>
-      <c r="T9" s="7" t="s">
+      <c r="S9" s="19"/>
+      <c r="T9" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="U9" s="8"/>
-    </row>
-    <row r="10" customFormat="false" ht="128.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="9" t="s">
+      <c r="U9" s="19"/>
+    </row>
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B10" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="25"/>
+      <c r="F10" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="24"/>
+      <c r="J10" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="K10" s="13"/>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="24"/>
+      <c r="L10" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="7" t="s">
+      <c r="M10" s="24"/>
+      <c r="N10" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="13"/>
-      <c r="P10" s="7" t="s">
+      <c r="O10" s="24"/>
+      <c r="P10" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="Q10" s="13" t="s">
+      <c r="Q10" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="R10" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="S10" s="13"/>
-      <c r="T10" s="7" t="s">
+      <c r="S10" s="24"/>
+      <c r="T10" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="U10" s="13"/>
+      <c r="U10" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4496,7 +4540,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="61" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/풍년 노래.xlsx
+++ b/sheets/민요/검수/풍년 노래.xlsx
@@ -4039,30 +4039,30 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="80.0" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -4086,7 +4086,7 @@
       <c r="T2" s="17"/>
       <c r="U2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="178.84" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>114</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="178.84" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>161</v>
       </c>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="178.84" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>176</v>
       </c>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="U5" s="19"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="178.84" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>179</v>
       </c>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="178.84" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>182</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="178.84" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>136</v>
       </c>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="U8" s="22"/>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="178.84" customHeight="true">
       <c r="B9" s="18" t="s">
         <v>186</v>
       </c>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="U9" s="19"/>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="178.84" customHeight="true">
       <c r="B10" s="20" t="s">
         <v>189</v>
       </c>
@@ -4540,7 +4540,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
